--- a/business_surveys/023_daily_transportation_fee_survey--business_surveys.xlsx
+++ b/business_surveys/023_daily_transportation_fee_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>Cost Frequency</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>cost_frequency</t>
+          <t>cost_frequency_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>Cost Frequency 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>Cost Vehicles</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Satisfaction</t>
+          <t>Satisfaction Mode</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -952,7 +952,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cost_frequency_choices</t>
+          <t>cost_frequency_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -969,7 +969,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cost_frequency_choices</t>
+          <t>cost_frequency_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
